--- a/outputs/59160.xlsx
+++ b/outputs/59160.xlsx
@@ -124,35 +124,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -397,21 +397,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="7" t="n">
-        <f aca="false">COUNTIFS($A$2:$A$11,D$1,$B$2:$B$11,D$2)</f>
-        <v>3</v>
+        <f aca="false">SUMPRODUCT((($B$2:$B$11="Yes")+($B$2:$B$11="No"))*($A$2:$A$11=$D$1))</f>
+        <v>5</v>
       </c>
       <c r="E3" s="8" t="n">
-        <f aca="false">COUNTIFS($A$2:$A$11,D$1,$B$2:$B$11,E$2)</f>
         <v>2</v>
       </c>
       <c r="F3" s="7" t="n">
-        <f aca="false">COUNTIFS($A$2:$A$11,F$1,$B$2:$B$11,F$2)</f>
-        <v>2</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <f aca="false">COUNTIFS($A$2:$A$11,F$1,$B$2:$B$11,G$2)</f>
-        <v>3</v>
-      </c>
+        <f aca="false">SUMPRODUCT((($B$2:$B$11="Yes")+($B$2:$B$11="No"))*($A$2:$A$11=$F$1))</f>
+        <v>5</v>
+      </c>
+      <c r="G3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
